--- a/data/trans_orig/IP25B_1_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP25B_1_R-Estudios-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10138</t>
+          <t>9472</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26290</t>
+          <t>26020</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>49,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7790</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19772</t>
+          <t>20388</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22077</t>
+          <t>22156</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43313</t>
+          <t>43832</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,55%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25993</t>
+          <t>26263</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42145</t>
+          <t>42811</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>41654</t>
+          <t>41038</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>53636</t>
+          <t>53330</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>66,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>70396</t>
+          <t>69877</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>91632</t>
+          <t>91553</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>80,52%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>93784</t>
+          <t>94947</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>195642</t>
+          <t>193177</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>119055</t>
+          <t>118220</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>174440</t>
+          <t>170252</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,47 +1123,47 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
+          <t>23,08%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>33,24%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>259430</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>223811</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>326113</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>26,95%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>23,25%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>34,06%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>259430</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>223027</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>334114</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>26,95%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>23,17%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>33,88%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>254709</t>
+          <t>257174</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>356567</t>
+          <t>355404</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>57,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>78,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>337692</t>
+          <t>341880</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>393077</t>
+          <t>393912</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,47 +1236,47 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
+          <t>76,92%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>703053</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>636370</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>738672</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>73,05%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>66,12%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>76,75%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1002</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>703053</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>628369</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>739456</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>73,05%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>65,29%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>76,83%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16241</t>
+          <t>16521</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31864</t>
+          <t>32259</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21984</t>
+          <t>21272</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41755</t>
+          <t>40687</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42452</t>
+          <t>43226</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>66680</t>
+          <t>66645</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,29%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>115079</t>
+          <t>114684</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>130702</t>
+          <t>130422</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>139747</t>
+          <t>140815</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>159518</t>
+          <t>160230</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>261765</t>
+          <t>261800</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>285993</t>
+          <t>285219</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>86,84%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>131769</t>
+          <t>132181</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>229914</t>
+          <t>231256</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>156383</t>
+          <t>157692</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>214708</t>
+          <t>216130</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>305590</t>
+          <t>303692</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>422051</t>
+          <t>415858</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>29,61%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>419663</t>
+          <t>418321</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>517808</t>
+          <t>517396</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>64,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>540352</t>
+          <t>538930</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>598677</t>
+          <t>597368</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>982587</t>
+          <t>988780</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1099048</t>
+          <t>1100946</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,95%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>78,38%</t>
         </is>
       </c>
     </row>
